--- a/tests/data/search_keywords.xlsx
+++ b/tests/data/search_keywords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ontwikkel\robot_framework_demo\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8B74E6-3173-4EA3-958A-97080F75E98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99826347-7B95-45BE-947A-39D2A75B8EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,16 +49,16 @@
     <t>Verify mango shows the no-results message.</t>
   </si>
   <si>
-    <t>keyword</t>
-  </si>
-  <si>
-    <t>amount_of_results</t>
-  </si>
-  <si>
     <t>Documentation</t>
   </si>
   <si>
-    <t>test_case</t>
+    <t>Test Case Description</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expectation</t>
   </si>
 </sst>
 </file>
@@ -409,16 +409,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">

--- a/tests/data/search_keywords.xlsx
+++ b/tests/data/search_keywords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ontwikkel\robot_framework_demo\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99826347-7B95-45BE-947A-39D2A75B8EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F49C396-5234-4381-A7C4-4E27BC7A85E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <si>
+    <t>Test Case Description</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expectation</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
   <si>
     <t>Search apple should show 3 results</t>
   </si>
@@ -28,6 +40,9 @@
     <t>apple</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Verify apple returns three visible product tiles.</t>
   </si>
   <si>
@@ -37,28 +52,49 @@
     <t>banana</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Verify banana returns one visible product tile.</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Verify an empty search leaves the visible catalog unchanged.</t>
+  </si>
+  <si>
+    <t>Search whitespace search should show the full catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Verify a whitespace-only search still shows the visible catalog.</t>
+  </si>
+  <si>
+    <t>Search at sign should show one result</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>Verify a special-character search can still narrow the catalog.</t>
+  </si>
+  <si>
     <t>Search mango should show no results</t>
   </si>
   <si>
     <t>mango</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Verify mango shows the no-results message.</t>
   </si>
   <si>
-    <t>Documentation</t>
-  </si>
-  <si>
-    <t>Test Case Description</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Expectation</t>
+    <t>Empty search should show the full catalog</t>
   </si>
 </sst>
 </file>
@@ -398,69 +434,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
